--- a/HW-Doc/MCU Pinout LQFP48.xlsx
+++ b/HW-Doc/MCU Pinout LQFP48.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Fki\Documents\Projekte\Etherbridge_custom\HW-Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEB8657-D779-49EE-B76F-AE397BA0E706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112E1323-90FC-4D4C-A3BC-AEB83AE3A61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2BCB3841-5261-458E-B6D1-67570C2DFED8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
   <si>
     <t>PinNr</t>
   </si>
@@ -359,9 +359,6 @@
     <t>Program Enable</t>
   </si>
   <si>
-    <t>Chip Select</t>
-  </si>
-  <si>
     <t>WZ_CLK</t>
   </si>
   <si>
@@ -390,6 +387,12 @@
   </si>
   <si>
     <t>MCU Pin</t>
+  </si>
+  <si>
+    <t>93LC86 Chip Select</t>
+  </si>
+  <si>
+    <t>USART1_RX</t>
   </si>
 </sst>
 </file>
@@ -950,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>76</v>
@@ -1402,7 +1405,7 @@
         <v>67</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>82</v>
@@ -1416,10 +1419,10 @@
         <v>38</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>39</v>
@@ -1433,7 +1436,7 @@
         <v>40</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>36</v>
@@ -1450,10 +1453,10 @@
         <v>41</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>17</v>
@@ -1467,7 +1470,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>43</v>
@@ -1484,7 +1487,7 @@
         <v>45</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>46</v>
@@ -1504,7 +1507,7 @@
         <v>48</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>39</v>
@@ -1547,7 +1550,7 @@
         <v>50</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>39</v>
@@ -1581,7 +1584,7 @@
         <v>69</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>39</v>
